--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onyxb\Desktop\ecquiz_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCA5EEB-A080-4EC7-9C24-BE89C45EBE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF848E6-328A-4910-9FA0-95D42708C83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4505" uniqueCount="2671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5005" uniqueCount="2961">
   <si>
     <t>section_id</t>
   </si>
@@ -12694,12 +12694,884 @@
   <si>
     <t>資本主義における資本の所有は私的所有であり、資本家の利潤追求による生産活動が行われる。</t>
   </si>
+  <si>
+    <t>keynes</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ケインズ</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>利子と物価の関係に注目し、貨幣数量説とは異なる貨幣論を展開したスウェーデンの経済学者は誰か。</t>
+  </si>
+  <si>
+    <t>クヌート・ヴィクセル</t>
+  </si>
+  <si>
+    <t>利子と物価の関係から物価変動を説明し、貨幣数量説とは異なる貨幣論を展開した。ケインズにも影響を与えた。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが提唱した、物価を一定に保つ利子率を何というか。</t>
+  </si>
+  <si>
+    <t>自然利子率</t>
+  </si>
+  <si>
+    <t>物価を一定に保つ利子率のこと。市場利子率との乖離が物価変動を引き起こすと考えた。</t>
+  </si>
+  <si>
+    <t>ヴィクセルは大学で当初何を学んだか。</t>
+  </si>
+  <si>
+    <t>大学では数学を学んだが、イギリス流の人口論に関心を持って経済学を学び始めた。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが経済学を学び始めるきっかけとなった、関心を持ったイギリス流の学問は何か。</t>
+  </si>
+  <si>
+    <t>イギリス流の人口論に関心を持ったことが、経済学を学ぶきっかけとなった。</t>
+  </si>
+  <si>
+    <t>ヴィクセルは奨学金を得て、どこで経済学を学んだか。</t>
+  </si>
+  <si>
+    <t>ヨーロッパ各国</t>
+  </si>
+  <si>
+    <t>奨学金を得てヨーロッパ各国で経済学を学んだ。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが聖書を風刺したことで問われた罪は何か。</t>
+  </si>
+  <si>
+    <t>冒涜の罪</t>
+  </si>
+  <si>
+    <t>学生を擁護するため聖書を風刺し、冒涜の罪で逮捕され2ヶ月の禁固を経験した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが聖書を風刺したのは、誰を擁護するためだったか。</t>
+  </si>
+  <si>
+    <t>学生</t>
+  </si>
+  <si>
+    <t>学生を擁護するために聖書を風刺したことが逮捕につながった。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが冒涜の罪で経験した禁固の期間はどれくらいか。</t>
+  </si>
+  <si>
+    <t>2ヶ月</t>
+  </si>
+  <si>
+    <t>冒涜の罪で逮捕され、2ヶ月の禁固を経験した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルがストックホルム大学で後進を指導して形成した学派を何というか。</t>
+  </si>
+  <si>
+    <t>ストックホルム学派</t>
+  </si>
+  <si>
+    <t>オリーンやミュルダールらを指導し、ストックホルム学派を形成した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルがストックホルム大学で指導した経済学者を2人答えよ。</t>
+  </si>
+  <si>
+    <t>ベルティル・オリーン、ギュンナー・ミュルダール</t>
+  </si>
+  <si>
+    <t>両者を指導してストックホルム学派を形成した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが自然利子率の概念を打ち出した著作のタイトルは何か。</t>
+  </si>
+  <si>
+    <t>『利子と物価』</t>
+  </si>
+  <si>
+    <t>この著作で自然利子率の概念と「物価の累積過程」を提示した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが『利子と物価』で提示した、物価が持続的に変動していく過程を何というか。</t>
+  </si>
+  <si>
+    <t>物価の累積過程</t>
+  </si>
+  <si>
+    <t>市場利子率と自然利子率の乖離が続く限り、物価が累積的に変動していくという議論。</t>
+  </si>
+  <si>
+    <t>ヴィクセルは限界革命の第何世代に属するとされるか。</t>
+  </si>
+  <si>
+    <t>第2世代</t>
+  </si>
+  <si>
+    <t>限界革命の第2世代に属し、限界生産性理論の明確化にも貢献した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルが明確化に貢献した、分配に関する理論は何か。</t>
+  </si>
+  <si>
+    <t>限界生産性理論</t>
+  </si>
+  <si>
+    <t>限界革命の第2世代として、限界生産性理論の明確化に貢献した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルの理論で、自然利子率が市場利子率を上回るとき、まず拡大する(貨幣供給の拡大につながる)ものは何か。</t>
+  </si>
+  <si>
+    <t>信用創造</t>
+  </si>
+  <si>
+    <t>自然利子率＞市場利子率 ⇒ 信用創造の拡大(貨幣供給の拡大) ⇒ 投資の拡大、という経路をたどる。</t>
+  </si>
+  <si>
+    <t>ヴィクセルの理論で、投資の拡大に続いて価格が上昇するのは何か。</t>
+  </si>
+  <si>
+    <t>生産資源</t>
+  </si>
+  <si>
+    <t>投資の拡大 ⇒ 生産資源の価格上昇 ⇒ 所得の上昇 ⇒ 消費者物価の上昇、という経路。</t>
+  </si>
+  <si>
+    <t>ヴィクセルの理論で、所得の上昇を経て最終的に上昇するのは何の物価か。</t>
+  </si>
+  <si>
+    <t>消費者物価</t>
+  </si>
+  <si>
+    <t>生産資源の価格上昇・所得の上昇を経て、最終的に消費者物価が上昇する。</t>
+  </si>
+  <si>
+    <t>貨幣量の変化が物価の変化を直接もたらすと考える理論を何というか。</t>
+  </si>
+  <si>
+    <t>貨幣量の変化→物価の変化と考える。ヴィクセルはこれと異なる貨幣理論を提示した。</t>
+  </si>
+  <si>
+    <t>ヴィクセルの貨幣理論では、物価変動の起点は市場利子率と何との乖離か。</t>
+  </si>
+  <si>
+    <t>市場利子率と自然利子率の乖離が、投資と貯蓄のバランスを変化させ、所得・物価へ波及する。</t>
+  </si>
+  <si>
+    <t>ヴィクセルの貨幣理論では、利子率の乖離がまず何のバランスを変化させるか。</t>
+  </si>
+  <si>
+    <t>投資と貯蓄</t>
+  </si>
+  <si>
+    <t>利子率の乖離→投資と貯蓄のバランス変化→所得の変化→物価の変化、という経路。</t>
+  </si>
+  <si>
+    <t>失業の理論を構築したイギリスの経済学者を、フルネームで答えよ。</t>
+  </si>
+  <si>
+    <t>ジョン・メイナード・ケインズ</t>
+  </si>
+  <si>
+    <t>多様な関心を持ち、政策論争に深く関わるなかで失業の理論を構築した。</t>
+  </si>
+  <si>
+    <t>ケインズの父で、ケンブリッジ大学の論理学者・経済学者であった人物は誰か。</t>
+  </si>
+  <si>
+    <t>ジョン・ネヴィル・ケインズ</t>
+  </si>
+  <si>
+    <t>ケインズの父であり、ケンブリッジ大学の論理学者・経済学者。</t>
+  </si>
+  <si>
+    <t>ケインズがケンブリッジ大学で学んだのは何か。</t>
+  </si>
+  <si>
+    <t>ケンブリッジで数学を学び、学年12位の成績で卒業した。</t>
+  </si>
+  <si>
+    <t>ケインズはケンブリッジ大学を学年何位の成績で卒業したか。</t>
+  </si>
+  <si>
+    <t>12位</t>
+  </si>
+  <si>
+    <t>学年12位の成績で卒業した。</t>
+  </si>
+  <si>
+    <t>ケインズは公務員試験で第何位になったか。</t>
+  </si>
+  <si>
+    <t>第2位</t>
+  </si>
+  <si>
+    <t>公務員試験で第2位となり、インド省に就職した。</t>
+  </si>
+  <si>
+    <t>ケインズが公務員として最初に就職した省庁はどこか。</t>
+  </si>
+  <si>
+    <t>インド省</t>
+  </si>
+  <si>
+    <t>公務員試験第2位でインド省に就職したが、2年で退職した。</t>
+  </si>
+  <si>
+    <t>ケインズはインド省を退職した後、ケンブリッジで何を教えたか。</t>
+  </si>
+  <si>
+    <t>インド省を2年で退職し、ケンブリッジに戻って経済学を教えた。</t>
+  </si>
+  <si>
+    <t>ケインズが1913年に出版した、インド省勤務の知識をもとにした著作は何か。</t>
+  </si>
+  <si>
+    <t>『インドの通貨および金融』</t>
+  </si>
+  <si>
+    <t>インド省勤務で得た知識をもとに出版した最初期の著作。</t>
+  </si>
+  <si>
+    <t>ケインズが学生時代に強く影響を受けた、直観主義を唱えた倫理学者は誰か。</t>
+  </si>
+  <si>
+    <t>G.E.ムーア</t>
+  </si>
+  <si>
+    <t>「善は直接に触れた時にのみ分かる」というムーアの直観主義の影響を強く受けた。</t>
+  </si>
+  <si>
+    <t>ムーアの直観主義では、善は「何」としてしか定義できないとされたか。</t>
+  </si>
+  <si>
+    <t>善</t>
+  </si>
+  <si>
+    <t>善は直接に触れた時にのみ分かるもので、善としてしか定義できないとされた。</t>
+  </si>
+  <si>
+    <t>「われわれの知っているあるいは想像しうる最も価値のあるもの」について論じたムーアの著作は何か。</t>
+  </si>
+  <si>
+    <t>『倫理学原理』</t>
+  </si>
+  <si>
+    <t>ケインズが影響を受けたムーアの著作。人間の交わりの楽しみと美しい対象の享受を最も価値あるものとした。</t>
+  </si>
+  <si>
+    <t>ケインズがベルサイユ条約締結交渉に参加した際の立場は何か。</t>
+  </si>
+  <si>
+    <t>財務省代表</t>
+  </si>
+  <si>
+    <t>財務省代表としてベルサイユ条約締結交渉に参加した。</t>
+  </si>
+  <si>
+    <t>ケインズを「時の人」にした、ベルサイユ条約交渉後に出版した著作は何か。</t>
+  </si>
+  <si>
+    <t>『平和の経済的帰結』</t>
+  </si>
+  <si>
+    <t>この著作の成功により時の人となった。</t>
+  </si>
+  <si>
+    <t>ケインズが著作の成功をもとに投資し、理事を務めた会社の業種は何か。</t>
+  </si>
+  <si>
+    <t>保険会社</t>
+  </si>
+  <si>
+    <t>著作の成功をもとに投資を行い、保険会社の理事を務めた。</t>
+  </si>
+  <si>
+    <t>ケインズが結婚した、ロシアのバレエ・ダンサーの名は何か。</t>
+  </si>
+  <si>
+    <t>リディア</t>
+  </si>
+  <si>
+    <t>ロシアのバレエ・ダンサー、リディアと結婚した。</t>
+  </si>
+  <si>
+    <t>ケインズが金本位制復帰を批判して出版した著作は何か。</t>
+  </si>
+  <si>
+    <t>『チャーチル氏の経済的帰結』</t>
+  </si>
+  <si>
+    <t>金本位制への復帰を批判した著作。</t>
+  </si>
+  <si>
+    <t>ケインズが政策要綱を共同執筆した政党は何か。</t>
+  </si>
+  <si>
+    <t>自由党</t>
+  </si>
+  <si>
+    <t>自由党の政策要綱を共同執筆した。</t>
+  </si>
+  <si>
+    <t>大恐慌の対策を議論するため、ケインズが代表を務めた委員会は何か。</t>
+  </si>
+  <si>
+    <t>経済諮問委員会</t>
+  </si>
+  <si>
+    <t>大恐慌の対策を議論する経済諮問委員会の代表を務めた。</t>
+  </si>
+  <si>
+    <t>ケインズの主著『一般理論』の正式なタイトルは何か。</t>
+  </si>
+  <si>
+    <t>『雇用、利子、および貨幣にかんする一般理論』</t>
+  </si>
+  <si>
+    <t>有効需要・乗数・流動性選好などの用語はこの著作に由来する。</t>
+  </si>
+  <si>
+    <t>20世紀初頭から半ばにかけ、定期的にロンドンに集まった文化人のグループを何というか。</t>
+  </si>
+  <si>
+    <t>ブルームズベリー・グループ</t>
+  </si>
+  <si>
+    <t>ケインズも関わった、小説家・評論家らからなる文化人のグループ。</t>
+  </si>
+  <si>
+    <t>ブルームズベリー・グループに属した小説家を2人答えよ。</t>
+  </si>
+  <si>
+    <t>バージニア・ウルフ、E.M.フォースター</t>
+  </si>
+  <si>
+    <t>いずれも小説家としてグループに属した。</t>
+  </si>
+  <si>
+    <t>ブルームズベリー・グループに属した伝記作家は誰か。</t>
+  </si>
+  <si>
+    <t>リットン・ストレイチー</t>
+  </si>
+  <si>
+    <t>伝記作家としてグループに属した。</t>
+  </si>
+  <si>
+    <t>ブルームズベリー・グループに属した評論家は誰か。</t>
+  </si>
+  <si>
+    <t>レナード・ウルフ</t>
+  </si>
+  <si>
+    <t>評論家としてグループに属した。</t>
+  </si>
+  <si>
+    <t>戦間期イギリスの失業率は、1920年代を通じておよそ何%前後だったか。</t>
+  </si>
+  <si>
+    <t>10%前後</t>
+  </si>
+  <si>
+    <t>1920年代を通じて10%前後で、第一次大戦前より一貫して高く、大恐慌時にさらに悪化した。</t>
+  </si>
+  <si>
+    <t>戦間期イギリスの失業率は、第一次大戦前と比べてどうだったか。</t>
+  </si>
+  <si>
+    <t>一貫して高かった</t>
+  </si>
+  <si>
+    <t>1920年代を通じて第一次大戦前より一貫して高く、大恐慌時にさらに悪化した。</t>
+  </si>
+  <si>
+    <t>イギリスが1925年に旧平価で復帰した制度は何か。</t>
+  </si>
+  <si>
+    <t>金本位制</t>
+  </si>
+  <si>
+    <t>旧平価での金本位制復帰は、戦間期イギリスの問題の一つとされた。</t>
+  </si>
+  <si>
+    <t>1926年にイギリスで起こった、労働運動の高まりを象徴する出来事は何か。</t>
+  </si>
+  <si>
+    <t>ゼネスト</t>
+  </si>
+  <si>
+    <t>1926年のゼネスト(ゼネラル・ストライキ)は労働運動の高まりを象徴した。</t>
+  </si>
+  <si>
+    <t>世界恐慌のきっかけとなった、1929年10月の出来事は何か。</t>
+  </si>
+  <si>
+    <t>ニューヨーク株式市場の暴落</t>
+  </si>
+  <si>
+    <t>これをきっかけに、国際金融システムの不均衡や政策対応の失敗により世界経済が大きく停滞した。</t>
+  </si>
+  <si>
+    <t>アメリカのGDP成長率が29年水準を回復した後、1938年に再び陥った不況を何と呼ぶか。</t>
+  </si>
+  <si>
+    <t>ローズベルト恐慌</t>
+  </si>
+  <si>
+    <t>GDP成長率は1936年にようやく29年水準を回復したが、1938年に不況へ転じた。</t>
+  </si>
+  <si>
+    <t>大恐慌対策としてニューディール政策を展開したアメリカの大統領は誰か。</t>
+  </si>
+  <si>
+    <t>F.D.ローズベルト</t>
+  </si>
+  <si>
+    <t>1933年に就任し、ニューディール政策を展開した。</t>
+  </si>
+  <si>
+    <t>ニューディール政策の一環として停止された通貨制度は何か。</t>
+  </si>
+  <si>
+    <t>金本位制の停止のほか、農業保護やカルテルの容認などが行われた。</t>
+  </si>
+  <si>
+    <t>ニューディール政策で、農業保護やカルテルの容認とともに強化された労働者の団体は何か。</t>
+  </si>
+  <si>
+    <t>労働組合</t>
+  </si>
+  <si>
+    <t>労働組合の強化がニューディール政策の一環として行われた。</t>
+  </si>
+  <si>
+    <t>ケインズが『一般理論』でマーシャルやピグーに与え、執拗に批判した呼称は何か。</t>
+  </si>
+  <si>
+    <t>古典派</t>
+  </si>
+  <si>
+    <t>マーシャルやピグーを「古典派」と名づけ、執拗に批判した。</t>
+  </si>
+  <si>
+    <t>ケインズがハロッドへの手紙で、批判が弱いと「何」に腕押しになると恐れたか。</t>
+  </si>
+  <si>
+    <t>のれん</t>
+  </si>
+  <si>
+    <t>十分強く批判しなければ「のれんに腕押し」になると述べ、騒ぎを起こしたいと記した。</t>
+  </si>
+  <si>
+    <t>有効需要・乗数・流動性選好などの用語の由来となった著作は何か。</t>
+  </si>
+  <si>
+    <t>『一般理論』</t>
+  </si>
+  <si>
+    <t>これらの用語は『雇用、利子、および貨幣にかんする一般理論』に由来する。</t>
+  </si>
+  <si>
+    <t>有効な投資先が減少し、民間需要だけでは完全雇用が実現できないというケインズの主張を何というか。</t>
+  </si>
+  <si>
+    <t>長期停滞論</t>
+  </si>
+  <si>
+    <t>『一般理論』で唱えた、有効な投資先の減少による完全雇用の未達を論じる主張。</t>
+  </si>
+  <si>
+    <t>ケインズによれば、供給力(生産力)が上昇しても、それが何されなければ所得にはならないか。</t>
+  </si>
+  <si>
+    <t>有効需要理論では、需要されなければ供給力の上昇は所得につながらない。</t>
+  </si>
+  <si>
+    <t>総消費支出と総投資支出を決定するとされる2つの概念は何か。</t>
+  </si>
+  <si>
+    <t>限界消費性向、資本の限界効率</t>
+  </si>
+  <si>
+    <t>この2概念で総消費支出と総投資支出が決定される(資料では「消費の限界性向」とも表記)。</t>
+  </si>
+  <si>
+    <t>資本の限界効率に影響する利子率は、何によって決定されるか。</t>
+  </si>
+  <si>
+    <t>貨幣的要因</t>
+  </si>
+  <si>
+    <t>利子率は貨幣的要因によって決定されるとした。</t>
+  </si>
+  <si>
+    <t>政府支出のない閉鎖経済で、総需要は消費支出と何の合計か。</t>
+  </si>
+  <si>
+    <t>投資支出</t>
+  </si>
+  <si>
+    <t>総需要＝消費支出＋投資支出、として示される。</t>
+  </si>
+  <si>
+    <t>所得が増えれば消費が増えるという関係を表す概念は何か。</t>
+  </si>
+  <si>
+    <t>限界消費性向</t>
+  </si>
+  <si>
+    <t>消費支出は限界消費性向によって決まる。</t>
+  </si>
+  <si>
+    <t>将来見通しが一定のとき、利子率が下がれば投資が増えるという関係を表す概念は何か。</t>
+  </si>
+  <si>
+    <t>資本の限界効率</t>
+  </si>
+  <si>
+    <t>投資支出は資本の限界効率によって決まる。</t>
+  </si>
+  <si>
+    <t>利子率は、貨幣供給と何の関係で決まるか。</t>
+  </si>
+  <si>
+    <t>貨幣需要</t>
+  </si>
+  <si>
+    <t>利子率は貨幣供給と貨幣需要の関係で決まる。</t>
+  </si>
+  <si>
+    <t>貨幣を保有しようとする欲求を表す、『一般理論』の3つの心理的概念の一つは何か。</t>
+  </si>
+  <si>
+    <t>流動性選好</t>
+  </si>
+  <si>
+    <t>限界消費性向・資本の限界効率とともに、『一般理論』の中心的な心理的概念。</t>
+  </si>
+  <si>
+    <t>流動性選好の3つの動機をすべて答えよ。</t>
+  </si>
+  <si>
+    <t>取引動機、予備的動機、投機的動機</t>
+  </si>
+  <si>
+    <t>この3つの動機によって貨幣需要(流動性選好)が説明される。</t>
+  </si>
+  <si>
+    <t>日々の経済取引に必要な貨幣を保有する動機を何というか。</t>
+  </si>
+  <si>
+    <t>取引動機</t>
+  </si>
+  <si>
+    <t>所得の増加関数とされる。</t>
+  </si>
+  <si>
+    <t>不意の支出に備えて貨幣を保有する動機を何というか。</t>
+  </si>
+  <si>
+    <t>予備的動機</t>
+  </si>
+  <si>
+    <t>債券投資の機会費用に関わる、貨幣保有の動機を何というか。</t>
+  </si>
+  <si>
+    <t>投機的動機</t>
+  </si>
+  <si>
+    <t>利子率の減少関数とされる。</t>
+  </si>
+  <si>
+    <t>投機的動機による流動性選好は、何の減少関数か。</t>
+  </si>
+  <si>
+    <t>利子率</t>
+  </si>
+  <si>
+    <t>利子率が上がると債券保有の機会費用が下がり、貨幣需要は減少する。</t>
+  </si>
+  <si>
+    <t>消費関数 C = c0 + cY における c は何を表すか。</t>
+  </si>
+  <si>
+    <t>国民所得が増えると1より小さい正の比率で消費が増える、その比率。</t>
+  </si>
+  <si>
+    <t>消費関数が C = c0 + cY のとき、貯蓄関数 S はどう表されるか。</t>
+  </si>
+  <si>
+    <t>S = (1-c)Y - c0</t>
+  </si>
+  <si>
+    <t>S = Y - C = Y - c0 - cY = (1-c)Y - c0。</t>
+  </si>
+  <si>
+    <t>将来見通しの変動がないとすれば、投資は利子率の何関数となるか。</t>
+  </si>
+  <si>
+    <t>減少関数</t>
+  </si>
+  <si>
+    <t>資本の限界効率により、投資は利子率の減少関数となる。</t>
+  </si>
+  <si>
+    <t>財市場(総生産と総支出)の均衡を表す曲線を何というか。</t>
+  </si>
+  <si>
+    <t>IS曲線</t>
+  </si>
+  <si>
+    <t>限界消費性向と資本の限界効率から導かれ、利子率と所得の負の関係を表す。</t>
+  </si>
+  <si>
+    <t>IS曲線では、利子率と所得の間にどのような関係が生じるか。</t>
+  </si>
+  <si>
+    <t>負の関係</t>
+  </si>
+  <si>
+    <t>投資関数と貯蓄関数を組み合わせると、利子率と所得の負の関係が生じる。</t>
+  </si>
+  <si>
+    <t>IS曲線が表す均衡条件を、投資Iと貯蓄Sを用いて式で答えよ。</t>
+  </si>
+  <si>
+    <t>I(r) = S(Y)</t>
+  </si>
+  <si>
+    <t>投資と貯蓄が均衡する、財市場の均衡条件。</t>
+  </si>
+  <si>
+    <t>貨幣市場(貨幣供給と貨幣需要)の均衡を表す曲線を何というか。</t>
+  </si>
+  <si>
+    <t>LM曲線</t>
+  </si>
+  <si>
+    <t>貨幣量Mと流動性選好L(Y,r)の均衡を表す。</t>
+  </si>
+  <si>
+    <t>LM曲線において、貨幣量はどのように決定されるとされるか。</t>
+  </si>
+  <si>
+    <t>外生的</t>
+  </si>
+  <si>
+    <t>貨幣量は外生的に決定される。利子率が上昇すれば、同じ貨幣量のもとで所得も上昇する。</t>
+  </si>
+  <si>
+    <t>LM曲線が表す関係を、貨幣量Mと流動性選好Lを用いて式で答えよ。</t>
+  </si>
+  <si>
+    <t>M = L(Y, r)</t>
+  </si>
+  <si>
+    <t>貨幣供給Mが貨幣需要(流動性選好)L(Y,r)に等しい状態を表す。</t>
+  </si>
+  <si>
+    <t>IS曲線とLM曲線の交点で決定される2つの変数は何か。</t>
+  </si>
+  <si>
+    <t>総所得と利子率</t>
+  </si>
+  <si>
+    <t>財市場の均衡(IS)と貨幣市場の均衡(LM)の交点で、総所得と利子率が決定される。</t>
+  </si>
+  <si>
+    <t>IS-LMモデルを1937年に提案した経済学者は誰か。</t>
+  </si>
+  <si>
+    <t>ジョン・ヒックス</t>
+  </si>
+  <si>
+    <t>『一般理論』出版の1年後に、ヒックス(1904-1989)が提案した。</t>
+  </si>
+  <si>
+    <t>古典派は、技術水準を所与とすれば自律的調整メカニズムのもとで何がつねに一定になると考えたか。</t>
+  </si>
+  <si>
+    <t>古典派では、経済の自律的調整メカニズムのもとで実質所得はつねに一定とされた。</t>
+  </si>
+  <si>
+    <t>古典派によれば、不況は消費財生産と何の生産の間の調整期間にすぎないか。</t>
+  </si>
+  <si>
+    <t>投資財(生産)</t>
+  </si>
+  <si>
+    <t>不況は消費財生産と投資財生産の間の調整期間であって、すぐに解消されるとした。</t>
+  </si>
+  <si>
+    <t>古典派では投資と貯蓄はどのような関係にあると想定されたか(ケインズが否定した点)。</t>
+  </si>
+  <si>
+    <t>独立</t>
+  </si>
+  <si>
+    <t>ケインズは、投資の減少が総所得を減らし貯蓄も減らすとして、投資と貯蓄の独立性を否定した。</t>
+  </si>
+  <si>
+    <t>ケインズ以前の経済学が主要な分析対象としたのは、何メカニズムか。</t>
+  </si>
+  <si>
+    <t>価格調整メカニズム</t>
+  </si>
+  <si>
+    <t>ケインズ以前は価格調整メカニズム、ケインズは総需要の決定メカニズムを分析対象とした。</t>
+  </si>
+  <si>
+    <t>ケインズが主要な分析対象としたのは、何の決定メカニズムか。</t>
+  </si>
+  <si>
+    <t>総需要</t>
+  </si>
+  <si>
+    <t>ケインズ以前の価格調整メカニズムに対し、ケインズは総需要の決定メカニズムを重視した。</t>
+  </si>
+  <si>
+    <t>ケインズ以前、均衡は何に収束すると考えられていたか。</t>
+  </si>
+  <si>
+    <t>完全雇用</t>
+  </si>
+  <si>
+    <t>ケインズは、総需要が不足すれば失業をともなって均衡すると考えた。</t>
+  </si>
+  <si>
+    <t>ケインズによれば、総需要が不足すると何をともなって均衡するか。</t>
+  </si>
+  <si>
+    <t>失業</t>
+  </si>
+  <si>
+    <t>完全雇用に収束するとは限らず、失業をともなう均衡が生じうるとした。</t>
+  </si>
+  <si>
+    <t>ケインズ以前、貨幣は生産活動に対しどのような性質を持つとされたか。</t>
+  </si>
+  <si>
+    <t>中立的</t>
+  </si>
+  <si>
+    <t>ケインズは、貨幣が利子率をつうじて総需要に影響すると考えた。</t>
+  </si>
+  <si>
+    <t>ケインズによれば、貨幣は何をつうじて総需要に影響するか。</t>
+  </si>
+  <si>
+    <t>貨幣は中立的ではなく、利子率をつうじて総需要に影響する。</t>
+  </si>
+  <si>
+    <t>ケインズ以前、不況への対策として何が主張されたか。</t>
+  </si>
+  <si>
+    <t>政府支出の削減</t>
+  </si>
+  <si>
+    <t>財政赤字が経済に混乱をもたらすと考えられ、政府支出の削減が主張された。</t>
+  </si>
+  <si>
+    <t>ケインズが不況対策として主張したのは何か。</t>
+  </si>
+  <si>
+    <t>政府支出の拡大</t>
+  </si>
+  <si>
+    <t>総需要を拡大し失業を減らすために、政府支出の拡大を主張した。</t>
+  </si>
+  <si>
+    <t>貯蓄から支出して雇用を増やす例えとして、ケインズが『一般理論』で用いた表現は何か。</t>
+  </si>
+  <si>
+    <t>「地面に穴を掘ること」</t>
+  </si>
+  <si>
+    <t>たとえ非生産的でも支出は雇用と有益な財・サービスの実質的な分け前を増やす、という趣旨。</t>
+  </si>
+  <si>
+    <t>利子率の低下で流動性選好が実質的に無限大になり、金融当局が利子率のコントロールを失う状態を何というか。</t>
+  </si>
+  <si>
+    <t>流動性の罠</t>
+  </si>
+  <si>
+    <t>ケインズは『一般理論』でこれを論じたが、これまでに起きた例は知らないと述べた。</t>
+  </si>
+  <si>
+    <t>ケインズが自然利子率を最初に定義した、『一般理論』以前の自身の著作は何か。</t>
+  </si>
+  <si>
+    <t>『貨幣論』</t>
+  </si>
+  <si>
+    <t>『貨幣論』でヴィクセルの「自然利子率」を拡張・明確化したものとして定義した。</t>
+  </si>
+  <si>
+    <t>ケインズは『一般理論』以前、各雇用水準に対して何が存在することを見逃していたと述べたか。</t>
+  </si>
+  <si>
+    <t>異なる自然利子率</t>
+  </si>
+  <si>
+    <t>各雇用水準に異なる自然利子率が存在すること、そして完全雇用以下でも均衡することを理解していなかったと反省している。</t>
+  </si>
+  <si>
+    <t>ヴィクセルの貨幣理論とケインズを比べると、ケインズは投資と貯蓄、貨幣需要と貨幣供給の2つの関係の相互依存によって何を決定したか。</t>
+  </si>
+  <si>
+    <t>利子率と所得</t>
+  </si>
+  <si>
+    <t>ヴィクセルが物価変動を論じたのに対し、ケインズは利子率と所得(・雇用)の決定を論じた。</t>
+  </si>
+  <si>
+    <t>ケインズが数理経済学を批判し、記号を用いた手法を何と呼んだか。</t>
+  </si>
+  <si>
+    <t>エセ数学(手法)</t>
+  </si>
+  <si>
+    <t>記号を用いたエセ数学手法は、異なる要因間の厳格な独立性を明示的に想定する点で欠点があると批判した。</t>
+  </si>
+  <si>
+    <t>数理経済学を批判したケインズに、その考えを学会で発表させようとした団体は何か。</t>
+  </si>
+  <si>
+    <t>エコノメトリック・ソサエティ</t>
+  </si>
+  <si>
+    <t>マーシャックらが、ケインズの新著の内容を明確な方法で説明させようとした。</t>
+  </si>
+  <si>
+    <t>フリッシュへの手紙で、ケインズの新著を説明する報告者候補として挙げられた2人は誰か。</t>
+  </si>
+  <si>
+    <t>カーン、ミード</t>
+  </si>
+  <si>
+    <t>マーシャックは、報告者としてカーンかミードに頼もうと考えた。</t>
+  </si>
+  <si>
+    <t>「ケインズ氏と古典派」という論文を書き、後にIS-LMモデルにつながる整理を行った経済学者は誰か。</t>
+  </si>
+  <si>
+    <t>ヒックス</t>
+  </si>
+  <si>
+    <t>1937年の論文「ケインズ氏と古典派」で、IS-LM的な整理を提示した。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12748,6 +13620,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -12767,7 +13645,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -12831,12 +13709,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -12866,6 +13759,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13171,7 +14067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E901"/>
+  <dimension ref="A1:E1001"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -28498,6 +29394,1706 @@
         <v>2376</v>
       </c>
     </row>
+    <row r="902" spans="1:5" ht="36">
+      <c r="A902" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B902" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C902" s="11" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D902" s="11" t="s">
+        <v>2674</v>
+      </c>
+      <c r="E902" s="11" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="903" spans="1:5" ht="36">
+      <c r="A903" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B903" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C903" s="11" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D903" s="11" t="s">
+        <v>2677</v>
+      </c>
+      <c r="E903" s="11" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="904" spans="1:5" ht="36">
+      <c r="A904" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B904" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C904" s="11" t="s">
+        <v>2679</v>
+      </c>
+      <c r="D904" s="11" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E904" s="11" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="905" spans="1:5" ht="36">
+      <c r="A905" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B905" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C905" s="11" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D905" s="11" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E905" s="11" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="906" spans="1:5" ht="18">
+      <c r="A906" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B906" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C906" s="11" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D906" s="11" t="s">
+        <v>2684</v>
+      </c>
+      <c r="E906" s="11" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="907" spans="1:5" ht="36">
+      <c r="A907" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B907" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C907" s="11" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D907" s="11" t="s">
+        <v>2687</v>
+      </c>
+      <c r="E907" s="11" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="908" spans="1:5" ht="18">
+      <c r="A908" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B908" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C908" s="11" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D908" s="11" t="s">
+        <v>2690</v>
+      </c>
+      <c r="E908" s="11" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="909" spans="1:5" ht="18">
+      <c r="A909" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B909" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C909" s="11" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D909" s="11" t="s">
+        <v>2693</v>
+      </c>
+      <c r="E909" s="11" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="910" spans="1:5" ht="36">
+      <c r="A910" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B910" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C910" s="11" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D910" s="11" t="s">
+        <v>2696</v>
+      </c>
+      <c r="E910" s="11" t="s">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="911" spans="1:5" ht="36">
+      <c r="A911" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B911" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C911" s="11" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D911" s="11" t="s">
+        <v>2699</v>
+      </c>
+      <c r="E911" s="11" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="912" spans="1:5" ht="36">
+      <c r="A912" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B912" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C912" s="11" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D912" s="11" t="s">
+        <v>2702</v>
+      </c>
+      <c r="E912" s="11" t="s">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="913" spans="1:5" ht="36">
+      <c r="A913" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B913" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C913" s="11" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D913" s="11" t="s">
+        <v>2705</v>
+      </c>
+      <c r="E913" s="11" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="914" spans="1:5" ht="36">
+      <c r="A914" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B914" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C914" s="11" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D914" s="11" t="s">
+        <v>2708</v>
+      </c>
+      <c r="E914" s="11" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="915" spans="1:5" ht="18">
+      <c r="A915" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B915" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C915" s="11" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D915" s="11" t="s">
+        <v>2711</v>
+      </c>
+      <c r="E915" s="11" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="916" spans="1:5" ht="36">
+      <c r="A916" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B916" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C916" s="11" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D916" s="11" t="s">
+        <v>2714</v>
+      </c>
+      <c r="E916" s="11" t="s">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="917" spans="1:5" ht="36">
+      <c r="A917" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B917" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C917" s="11" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D917" s="11" t="s">
+        <v>2717</v>
+      </c>
+      <c r="E917" s="11" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="918" spans="1:5" ht="36">
+      <c r="A918" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B918" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C918" s="11" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D918" s="11" t="s">
+        <v>2720</v>
+      </c>
+      <c r="E918" s="11" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="919" spans="1:5" ht="36">
+      <c r="A919" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B919" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C919" s="11" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D919" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E919" s="11" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="920" spans="1:5" ht="36">
+      <c r="A920" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B920" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C920" s="11" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D920" s="11" t="s">
+        <v>2677</v>
+      </c>
+      <c r="E920" s="11" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="921" spans="1:5" ht="36">
+      <c r="A921" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B921" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C921" s="11" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D921" s="11" t="s">
+        <v>2727</v>
+      </c>
+      <c r="E921" s="11" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="922" spans="1:5" ht="36">
+      <c r="A922" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B922" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C922" s="11" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D922" s="11" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E922" s="11" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="923" spans="1:5" ht="36">
+      <c r="A923" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B923" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C923" s="11" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D923" s="11" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E923" s="11" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="924" spans="1:5" ht="18">
+      <c r="A924" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B924" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C924" s="11" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D924" s="11" t="s">
+        <v>1874</v>
+      </c>
+      <c r="E924" s="11" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="925" spans="1:5" ht="18">
+      <c r="A925" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B925" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C925" s="11" t="s">
+        <v>2737</v>
+      </c>
+      <c r="D925" s="11" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E925" s="11" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="926" spans="1:5" ht="18">
+      <c r="A926" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B926" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C926" s="11" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D926" s="11" t="s">
+        <v>2741</v>
+      </c>
+      <c r="E926" s="11" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="927" spans="1:5" ht="18">
+      <c r="A927" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B927" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C927" s="11" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D927" s="11" t="s">
+        <v>2744</v>
+      </c>
+      <c r="E927" s="11" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="928" spans="1:5" ht="36">
+      <c r="A928" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B928" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C928" s="11" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D928" s="11" t="s">
+        <v>2461</v>
+      </c>
+      <c r="E928" s="11" t="s">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="929" spans="1:5" ht="36">
+      <c r="A929" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B929" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C929" s="11" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D929" s="11" t="s">
+        <v>2749</v>
+      </c>
+      <c r="E929" s="11" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="930" spans="1:5" ht="36">
+      <c r="A930" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B930" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C930" s="11" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D930" s="11" t="s">
+        <v>2752</v>
+      </c>
+      <c r="E930" s="11" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="931" spans="1:5" ht="36">
+      <c r="A931" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B931" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C931" s="11" t="s">
+        <v>2754</v>
+      </c>
+      <c r="D931" s="11" t="s">
+        <v>2755</v>
+      </c>
+      <c r="E931" s="11" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="932" spans="1:5" ht="36">
+      <c r="A932" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B932" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C932" s="11" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D932" s="11" t="s">
+        <v>2758</v>
+      </c>
+      <c r="E932" s="11" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="933" spans="1:5" ht="18">
+      <c r="A933" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B933" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C933" s="11" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D933" s="11" t="s">
+        <v>2761</v>
+      </c>
+      <c r="E933" s="11" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="934" spans="1:5" ht="36">
+      <c r="A934" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B934" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C934" s="11" t="s">
+        <v>2763</v>
+      </c>
+      <c r="D934" s="11" t="s">
+        <v>2764</v>
+      </c>
+      <c r="E934" s="11" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="935" spans="1:5" ht="36">
+      <c r="A935" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B935" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C935" s="11" t="s">
+        <v>2766</v>
+      </c>
+      <c r="D935" s="11" t="s">
+        <v>2767</v>
+      </c>
+      <c r="E935" s="11" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="936" spans="1:5" ht="18">
+      <c r="A936" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B936" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C936" s="11" t="s">
+        <v>2769</v>
+      </c>
+      <c r="D936" s="11" t="s">
+        <v>2770</v>
+      </c>
+      <c r="E936" s="11" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="937" spans="1:5" ht="18">
+      <c r="A937" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B937" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C937" s="11" t="s">
+        <v>2772</v>
+      </c>
+      <c r="D937" s="11" t="s">
+        <v>2773</v>
+      </c>
+      <c r="E937" s="11" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="938" spans="1:5" ht="18">
+      <c r="A938" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B938" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C938" s="11" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D938" s="11" t="s">
+        <v>2776</v>
+      </c>
+      <c r="E938" s="11" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="939" spans="1:5" ht="36">
+      <c r="A939" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B939" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C939" s="11" t="s">
+        <v>2778</v>
+      </c>
+      <c r="D939" s="11" t="s">
+        <v>2779</v>
+      </c>
+      <c r="E939" s="11" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="940" spans="1:5" ht="36">
+      <c r="A940" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B940" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C940" s="11" t="s">
+        <v>2781</v>
+      </c>
+      <c r="D940" s="11" t="s">
+        <v>2782</v>
+      </c>
+      <c r="E940" s="11" t="s">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="941" spans="1:5" ht="36">
+      <c r="A941" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B941" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C941" s="11" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D941" s="11" t="s">
+        <v>2785</v>
+      </c>
+      <c r="E941" s="11" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="942" spans="1:5" ht="36">
+      <c r="A942" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B942" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C942" s="11" t="s">
+        <v>2787</v>
+      </c>
+      <c r="D942" s="11" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E942" s="11" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="943" spans="1:5" ht="18">
+      <c r="A943" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B943" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C943" s="11" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D943" s="11" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E943" s="11" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="944" spans="1:5" ht="18">
+      <c r="A944" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B944" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C944" s="11" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D944" s="11" t="s">
+        <v>2794</v>
+      </c>
+      <c r="E944" s="11" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="945" spans="1:5" ht="36">
+      <c r="A945" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B945" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C945" s="11" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D945" s="11" t="s">
+        <v>2797</v>
+      </c>
+      <c r="E945" s="11" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="946" spans="1:5" ht="36">
+      <c r="A946" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B946" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C946" s="11" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D946" s="11" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E946" s="11" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="947" spans="1:5" ht="36">
+      <c r="A947" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B947" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C947" s="11" t="s">
+        <v>2802</v>
+      </c>
+      <c r="D947" s="11" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E947" s="11" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="948" spans="1:5" ht="36">
+      <c r="A948" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B948" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C948" s="11" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D948" s="11" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E948" s="11" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="949" spans="1:5" ht="36">
+      <c r="A949" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B949" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C949" s="11" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D949" s="11" t="s">
+        <v>2809</v>
+      </c>
+      <c r="E949" s="11" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="950" spans="1:5" ht="36">
+      <c r="A950" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B950" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C950" s="11" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D950" s="11" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E950" s="11" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="951" spans="1:5" ht="36">
+      <c r="A951" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B951" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C951" s="11" t="s">
+        <v>2814</v>
+      </c>
+      <c r="D951" s="11" t="s">
+        <v>2815</v>
+      </c>
+      <c r="E951" s="11" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="952" spans="1:5" ht="36">
+      <c r="A952" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B952" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C952" s="11" t="s">
+        <v>2817</v>
+      </c>
+      <c r="D952" s="11" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E952" s="11" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="953" spans="1:5" ht="36">
+      <c r="A953" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B953" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C953" s="11" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D953" s="11" t="s">
+        <v>2820</v>
+      </c>
+      <c r="E953" s="11" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="954" spans="1:5" ht="36">
+      <c r="A954" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B954" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C954" s="11" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D954" s="11" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E954" s="11" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="955" spans="1:5" ht="36">
+      <c r="A955" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B955" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C955" s="11" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D955" s="11" t="s">
+        <v>2826</v>
+      </c>
+      <c r="E955" s="11" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="956" spans="1:5" ht="36">
+      <c r="A956" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B956" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C956" s="11" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D956" s="11" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E956" s="11" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="957" spans="1:5" ht="36">
+      <c r="A957" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B957" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C957" s="11" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D957" s="11" t="s">
+        <v>2832</v>
+      </c>
+      <c r="E957" s="11" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="958" spans="1:5" ht="36">
+      <c r="A958" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B958" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C958" s="11" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D958" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E958" s="11" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="959" spans="1:5" ht="36">
+      <c r="A959" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B959" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C959" s="11" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D959" s="11" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E959" s="11" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="960" spans="1:5" ht="18">
+      <c r="A960" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B960" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C960" s="11" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D960" s="11" t="s">
+        <v>2840</v>
+      </c>
+      <c r="E960" s="11" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="961" spans="1:5" ht="18">
+      <c r="A961" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B961" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C961" s="11" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D961" s="11" t="s">
+        <v>2843</v>
+      </c>
+      <c r="E961" s="11" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="962" spans="1:5" ht="18">
+      <c r="A962" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B962" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C962" s="11" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D962" s="11" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E962" s="11" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="963" spans="1:5" ht="36">
+      <c r="A963" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B963" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C963" s="11" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D963" s="11" t="s">
+        <v>2849</v>
+      </c>
+      <c r="E963" s="11" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="964" spans="1:5" ht="18">
+      <c r="A964" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B964" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C964" s="11" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D964" s="11" t="s">
+        <v>2852</v>
+      </c>
+      <c r="E964" s="11" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="965" spans="1:5" ht="36">
+      <c r="A965" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B965" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C965" s="11" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D965" s="11" t="s">
+        <v>2855</v>
+      </c>
+      <c r="E965" s="11" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="966" spans="1:5" ht="36">
+      <c r="A966" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B966" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C966" s="11" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D966" s="11" t="s">
+        <v>2858</v>
+      </c>
+      <c r="E966" s="11" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="967" spans="1:5" ht="18">
+      <c r="A967" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B967" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C967" s="11" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D967" s="11" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E967" s="11" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="968" spans="1:5" ht="18">
+      <c r="A968" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B968" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C968" s="11" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D968" s="11" t="s">
+        <v>2864</v>
+      </c>
+      <c r="E968" s="11" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="969" spans="1:5" ht="18">
+      <c r="A969" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B969" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C969" s="11" t="s">
+        <v>2865</v>
+      </c>
+      <c r="D969" s="11" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E969" s="11" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="970" spans="1:5" ht="36">
+      <c r="A970" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B970" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C970" s="11" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D970" s="11" t="s">
+        <v>2869</v>
+      </c>
+      <c r="E970" s="11" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="971" spans="1:5" ht="36">
+      <c r="A971" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B971" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C971" s="11" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D971" s="11" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E971" s="11" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="972" spans="1:5" ht="18">
+      <c r="A972" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B972" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C972" s="11" t="s">
+        <v>2873</v>
+      </c>
+      <c r="D972" s="11" t="s">
+        <v>2874</v>
+      </c>
+      <c r="E972" s="11" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="973" spans="1:5" ht="36">
+      <c r="A973" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B973" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C973" s="11" t="s">
+        <v>2876</v>
+      </c>
+      <c r="D973" s="11" t="s">
+        <v>2877</v>
+      </c>
+      <c r="E973" s="11" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="974" spans="1:5" ht="36">
+      <c r="A974" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B974" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C974" s="11" t="s">
+        <v>2879</v>
+      </c>
+      <c r="D974" s="11" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E974" s="11" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="975" spans="1:5" ht="36">
+      <c r="A975" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B975" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C975" s="11" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D975" s="11" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E975" s="11" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="976" spans="1:5" ht="18">
+      <c r="A976" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B976" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C976" s="11" t="s">
+        <v>2885</v>
+      </c>
+      <c r="D976" s="11" t="s">
+        <v>2886</v>
+      </c>
+      <c r="E976" s="11" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="977" spans="1:5" ht="18">
+      <c r="A977" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B977" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C977" s="11" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D977" s="11" t="s">
+        <v>2889</v>
+      </c>
+      <c r="E977" s="11" t="s">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="978" spans="1:5" ht="36">
+      <c r="A978" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B978" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C978" s="11" t="s">
+        <v>2891</v>
+      </c>
+      <c r="D978" s="11" t="s">
+        <v>2892</v>
+      </c>
+      <c r="E978" s="11" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="979" spans="1:5" ht="36">
+      <c r="A979" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B979" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C979" s="11" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D979" s="11" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E979" s="11" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="980" spans="1:5" ht="36">
+      <c r="A980" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B980" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C980" s="11" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D980" s="11" t="s">
+        <v>2898</v>
+      </c>
+      <c r="E980" s="11" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="981" spans="1:5" ht="18">
+      <c r="A981" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B981" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C981" s="11" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D981" s="11" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E981" s="11" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="982" spans="1:5" ht="36">
+      <c r="A982" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B982" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C982" s="11" t="s">
+        <v>2903</v>
+      </c>
+      <c r="D982" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E982" s="11" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="983" spans="1:5" ht="36">
+      <c r="A983" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B983" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C983" s="11" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D983" s="11" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E983" s="11" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="984" spans="1:5" ht="36">
+      <c r="A984" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B984" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C984" s="11" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D984" s="11" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E984" s="11" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="985" spans="1:5" ht="36">
+      <c r="A985" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B985" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C985" s="11" t="s">
+        <v>2911</v>
+      </c>
+      <c r="D985" s="11" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E985" s="11" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="986" spans="1:5" ht="36">
+      <c r="A986" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B986" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C986" s="11" t="s">
+        <v>2914</v>
+      </c>
+      <c r="D986" s="11" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E986" s="11" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="987" spans="1:5" ht="36">
+      <c r="A987" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B987" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C987" s="11" t="s">
+        <v>2917</v>
+      </c>
+      <c r="D987" s="11" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E987" s="11" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="988" spans="1:5" ht="36">
+      <c r="A988" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B988" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C988" s="11" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D988" s="11" t="s">
+        <v>2921</v>
+      </c>
+      <c r="E988" s="11" t="s">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="989" spans="1:5" ht="36">
+      <c r="A989" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B989" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C989" s="11" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D989" s="11" t="s">
+        <v>2924</v>
+      </c>
+      <c r="E989" s="11" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="990" spans="1:5" ht="18">
+      <c r="A990" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B990" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C990" s="11" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D990" s="11" t="s">
+        <v>2869</v>
+      </c>
+      <c r="E990" s="11" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="991" spans="1:5" ht="36">
+      <c r="A991" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B991" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C991" s="11" t="s">
+        <v>2928</v>
+      </c>
+      <c r="D991" s="11" t="s">
+        <v>2929</v>
+      </c>
+      <c r="E991" s="11" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="992" spans="1:5" ht="36">
+      <c r="A992" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B992" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C992" s="11" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D992" s="11" t="s">
+        <v>2932</v>
+      </c>
+      <c r="E992" s="11" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="993" spans="1:5" ht="36">
+      <c r="A993" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B993" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C993" s="11" t="s">
+        <v>2934</v>
+      </c>
+      <c r="D993" s="11" t="s">
+        <v>2935</v>
+      </c>
+      <c r="E993" s="11" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="994" spans="1:5" ht="36">
+      <c r="A994" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B994" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C994" s="11" t="s">
+        <v>2937</v>
+      </c>
+      <c r="D994" s="11" t="s">
+        <v>2938</v>
+      </c>
+      <c r="E994" s="11" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="995" spans="1:5" ht="36">
+      <c r="A995" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B995" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C995" s="11" t="s">
+        <v>2940</v>
+      </c>
+      <c r="D995" s="11" t="s">
+        <v>2941</v>
+      </c>
+      <c r="E995" s="11" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="996" spans="1:5" ht="36">
+      <c r="A996" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B996" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C996" s="11" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D996" s="11" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E996" s="11" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="997" spans="1:5" ht="54">
+      <c r="A997" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B997" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C997" s="11" t="s">
+        <v>2946</v>
+      </c>
+      <c r="D997" s="11" t="s">
+        <v>2947</v>
+      </c>
+      <c r="E997" s="11" t="s">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="998" spans="1:5" ht="36">
+      <c r="A998" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B998" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C998" s="11" t="s">
+        <v>2949</v>
+      </c>
+      <c r="D998" s="11" t="s">
+        <v>2950</v>
+      </c>
+      <c r="E998" s="11" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="999" spans="1:5" ht="36">
+      <c r="A999" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B999" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C999" s="11" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D999" s="11" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E999" s="11" t="s">
+        <v>2954</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:5" ht="36">
+      <c r="A1000" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B1000" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C1000" s="11" t="s">
+        <v>2955</v>
+      </c>
+      <c r="D1000" s="11" t="s">
+        <v>2956</v>
+      </c>
+      <c r="E1000" s="11" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:5" ht="36">
+      <c r="A1001" s="9" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B1001" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C1001" s="11" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D1001" s="11" t="s">
+        <v>2959</v>
+      </c>
+      <c r="E1001" s="11" t="s">
+        <v>2960</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
